--- a/artfynd/A 28066-2026 artfynd.xlsx
+++ b/artfynd/A 28066-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,27 +680,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99778396</v>
+        <v>137393778</v>
       </c>
       <c r="B2" t="n">
-        <v>58636</v>
+        <v>58048</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,27 +710,23 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gräsmalnsvägen, Hls</t>
+          <t>Gräsmaln, Hudiksvalls kommun, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613926</v>
+        <v>613781</v>
       </c>
       <c r="R2" t="n">
-        <v>6844955</v>
+        <v>6845010</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,27 +753,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-04-10</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-04-10</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Uppskattat antal,kanske flera.</t>
+          <t>Noterade ett antal hålträd i skogen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,24 +788,24 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Malte Gallon</t>
+          <t>Charliene Kiffer Goude</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Malte Gallon</t>
+          <t>Charliene Kiffer Goude</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99778396</t>
+          <t>https://artportalen.se/Sighting/137393778</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107134339</v>
+        <v>99778396</v>
       </c>
       <c r="B3" t="n">
         <v>58636</v>
@@ -839,7 +835,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -852,17 +848,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gräsmalnsvägen, Hudiksvall, Hls</t>
+          <t>Gräsmalnsvägen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>614071</v>
+        <v>613926</v>
       </c>
       <c r="R3" t="n">
-        <v>6844938</v>
+        <v>6844955</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +882,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
+          <t>2022-04-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -896,12 +892,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
+          <t>2022-04-10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
           <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Uppskattat antal,kanske flera.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,54 +917,54 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Narfström</t>
+          <t>Malte Gallon</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Narfström</t>
+          <t>Malte Gallon</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107134339</t>
+          <t>https://artportalen.se/Sighting/99778396</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107134340</v>
+        <v>107134339</v>
       </c>
       <c r="B4" t="n">
-        <v>58676</v>
+        <v>58636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -1050,6 +1051,130 @@
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107134339</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>107134340</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gräsmalnsvägen, Hudiksvall, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>614071</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6844938</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hälsingtuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Fredrik Narfström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Fredrik Narfström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/107134340</t>
         </is>
@@ -1060,6 +1185,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28066-2026 artfynd.xlsx
+++ b/artfynd/A 28066-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137393778</v>
       </c>
       <c r="B2" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
